--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Rapeseed Oil (1514.11)/China.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Rapeseed Oil (1514.11)/China.xlsx
@@ -2953,10 +2953,10 @@
       </c>
       <c r="B5" s="2">
         <f t="shared" si="0"/>
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="C5" s="2">
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="D5" s="2">
         <v>900</v>
@@ -3091,11 +3091,11 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
-        <v>2080</v>
+        <v>2090</v>
       </c>
       <c r="D15" s="5">
         <f t="shared" si="1"/>
